--- a/Experiments/outputs/scenario_7.xlsx
+++ b/Experiments/outputs/scenario_7.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1142.765763176633</v>
+        <v>1244.595807913093</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8209729194641113</v>
+        <v>1.751189708709717</v>
       </c>
       <c r="E2" t="n">
-        <v>422</v>
+        <v>390</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="G2" t="n">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="H2" t="n">
-        <v>2398.114761688685</v>
+        <v>2950.45401717953</v>
       </c>
       <c r="I2" t="n">
-        <v>1.999069213867188</v>
+        <v>17.44600391387939</v>
       </c>
       <c r="J2" t="n">
-        <v>476</v>
+        <v>430</v>
       </c>
       <c r="K2" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="L2" t="n">
-        <v>521</v>
+        <v>785</v>
       </c>
       <c r="M2" t="n">
-        <v>6692.691898982155</v>
+        <v>7043.756298997811</v>
       </c>
       <c r="N2" t="n">
-        <v>5.106823921203613</v>
+        <v>7.177636861801147</v>
       </c>
       <c r="O2" t="n">
-        <v>1905</v>
+        <v>1745</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>6022</v>
+        <v>5644</v>
       </c>
       <c r="R2" t="n">
-        <v>0.829251700149169</v>
+        <v>0.8233051009884917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6416815837505687</v>
+        <v>0.581124915182071</v>
       </c>
     </row>
     <row r="3">
@@ -591,55 +591,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1151.448255050841</v>
+        <v>1223.880380152835</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5507903099060059</v>
+        <v>0.8183672428131104</v>
       </c>
       <c r="E3" t="n">
-        <v>380</v>
+        <v>349</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="H3" t="n">
-        <v>2532.014466548047</v>
+        <v>2867.031893781275</v>
       </c>
       <c r="I3" t="n">
-        <v>1.729428052902222</v>
+        <v>12.74685907363892</v>
       </c>
       <c r="J3" t="n">
-        <v>464</v>
+        <v>426</v>
       </c>
       <c r="K3" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="L3" t="n">
-        <v>517</v>
+        <v>756</v>
       </c>
       <c r="M3" t="n">
-        <v>6730.28285014986</v>
+        <v>6790.989516691422</v>
       </c>
       <c r="N3" t="n">
-        <v>5.131031036376953</v>
+        <v>5.813399076461792</v>
       </c>
       <c r="O3" t="n">
-        <v>1835</v>
+        <v>1700</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>5938</v>
+        <v>5502</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8289153248551504</v>
+        <v>0.8197787852352465</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6237878075968728</v>
+        <v>0.5778182418431863</v>
       </c>
     </row>
     <row r="4">
@@ -652,55 +652,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1155.934546739114</v>
+        <v>1304.859426584262</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6087291240692139</v>
+        <v>1.087017059326172</v>
       </c>
       <c r="E4" t="n">
-        <v>418</v>
+        <v>376</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
         <v>138</v>
       </c>
       <c r="H4" t="n">
-        <v>2435.696919263992</v>
+        <v>3036.51535876485</v>
       </c>
       <c r="I4" t="n">
-        <v>1.576366186141968</v>
+        <v>14.47802209854126</v>
       </c>
       <c r="J4" t="n">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="K4" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="L4" t="n">
-        <v>506</v>
+        <v>810</v>
       </c>
       <c r="M4" t="n">
-        <v>6716.028870182933</v>
+        <v>6875.682995741851</v>
       </c>
       <c r="N4" t="n">
-        <v>4.305844306945801</v>
+        <v>5.212942838668823</v>
       </c>
       <c r="O4" t="n">
-        <v>1917</v>
+        <v>1761</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>6177</v>
+        <v>5624</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8278842201124089</v>
+        <v>0.8102211187757831</v>
       </c>
       <c r="S4" t="n">
-        <v>0.637330784851488</v>
+        <v>0.5583689124927108</v>
       </c>
     </row>
     <row r="5">
@@ -713,55 +713,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1100.147230384397</v>
+        <v>1377.939481077319</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4425339698791504</v>
+        <v>0.9994208812713623</v>
       </c>
       <c r="E5" t="n">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="G5" t="n">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H5" t="n">
-        <v>2370.224138470017</v>
+        <v>2500.708976631747</v>
       </c>
       <c r="I5" t="n">
-        <v>2.311470985412598</v>
+        <v>8.664873838424683</v>
       </c>
       <c r="J5" t="n">
-        <v>448</v>
+        <v>401</v>
       </c>
       <c r="K5" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="L5" t="n">
-        <v>500</v>
+        <v>677</v>
       </c>
       <c r="M5" t="n">
-        <v>6732.897436393322</v>
+        <v>6962.832322441252</v>
       </c>
       <c r="N5" t="n">
-        <v>4.624184131622314</v>
+        <v>9.05760931968689</v>
       </c>
       <c r="O5" t="n">
-        <v>1852</v>
+        <v>1711</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>5862</v>
+        <v>5466</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8366012194931454</v>
+        <v>0.8021007232019344</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6479637242566257</v>
+        <v>0.6408488872305677</v>
       </c>
     </row>
     <row r="6">
@@ -774,55 +774,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1070.681983476695</v>
+        <v>1334.329543584515</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5582258701324463</v>
+        <v>0.9147069454193115</v>
       </c>
       <c r="E6" t="n">
-        <v>399</v>
+        <v>363</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H6" t="n">
-        <v>2328.419065411862</v>
+        <v>2955.262320249927</v>
       </c>
       <c r="I6" t="n">
-        <v>1.525168895721436</v>
+        <v>14.84217691421509</v>
       </c>
       <c r="J6" t="n">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="K6" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="L6" t="n">
-        <v>478</v>
+        <v>772</v>
       </c>
       <c r="M6" t="n">
-        <v>6758.738370389325</v>
+        <v>7012.916011940471</v>
       </c>
       <c r="N6" t="n">
-        <v>5.185616970062256</v>
+        <v>5.782921075820923</v>
       </c>
       <c r="O6" t="n">
-        <v>1835</v>
+        <v>1730</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>5896</v>
+        <v>5618</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8415855260550617</v>
+        <v>0.809732564697391</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6554950143339049</v>
+        <v>0.5785972175884925</v>
       </c>
     </row>
     <row r="7">
@@ -835,55 +835,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1115.78036792254</v>
+        <v>1272.895936522946</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8436203002929688</v>
+        <v>0.7964339256286621</v>
       </c>
       <c r="E7" t="n">
-        <v>397</v>
+        <v>375</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="H7" t="n">
-        <v>2340.496046365603</v>
+        <v>2994.961198848893</v>
       </c>
       <c r="I7" t="n">
-        <v>1.555069923400879</v>
+        <v>15.53120398521423</v>
       </c>
       <c r="J7" t="n">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="K7" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L7" t="n">
-        <v>535</v>
+        <v>808</v>
       </c>
       <c r="M7" t="n">
-        <v>6808.974931016968</v>
+        <v>6994.804938005295</v>
       </c>
       <c r="N7" t="n">
-        <v>5.014090776443481</v>
+        <v>6.087238073348999</v>
       </c>
       <c r="O7" t="n">
-        <v>1833</v>
+        <v>1747</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
-        <v>5841</v>
+        <v>5708</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8361309331835225</v>
+        <v>0.8180226685655172</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6562630836392235</v>
+        <v>0.5718306335354414</v>
       </c>
     </row>
     <row r="8">
@@ -896,55 +896,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1242.810230448454</v>
+        <v>1226.657861316856</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5141220092773438</v>
+        <v>1.136071920394897</v>
       </c>
       <c r="E8" t="n">
-        <v>421</v>
+        <v>367</v>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="H8" t="n">
-        <v>2411.884585840758</v>
+        <v>2959.001324186247</v>
       </c>
       <c r="I8" t="n">
-        <v>1.703421831130981</v>
+        <v>15.43182182312012</v>
       </c>
       <c r="J8" t="n">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="K8" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L8" t="n">
-        <v>505</v>
+        <v>795</v>
       </c>
       <c r="M8" t="n">
-        <v>6772.898502219145</v>
+        <v>6970.107561612598</v>
       </c>
       <c r="N8" t="n">
-        <v>4.330609083175659</v>
+        <v>6.384413957595825</v>
       </c>
       <c r="O8" t="n">
-        <v>1880</v>
+        <v>1707</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>5994</v>
+        <v>5612</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8165024575458726</v>
+        <v>0.8240116310295421</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6438918160296508</v>
+        <v>0.5754726454319372</v>
       </c>
     </row>
     <row r="9">
@@ -957,55 +957,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1133.644887991577</v>
+        <v>1250.638338648174</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4366672039031982</v>
+        <v>0.8895165920257568</v>
       </c>
       <c r="E9" t="n">
-        <v>355</v>
+        <v>392</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="H9" t="n">
-        <v>2371.284755852977</v>
+        <v>2810.558174956052</v>
       </c>
       <c r="I9" t="n">
-        <v>1.916144132614136</v>
+        <v>10.20192265510559</v>
       </c>
       <c r="J9" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="K9" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="L9" t="n">
-        <v>510</v>
+        <v>777</v>
       </c>
       <c r="M9" t="n">
-        <v>6696.644306116001</v>
+        <v>6985.840623984408</v>
       </c>
       <c r="N9" t="n">
-        <v>4.491292953491211</v>
+        <v>7.554008960723877</v>
       </c>
       <c r="O9" t="n">
-        <v>1831</v>
+        <v>1736</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5888</v>
+        <v>5690</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8307144838264403</v>
+        <v>0.8209752546666508</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6458995509605762</v>
+        <v>0.5976778849911641</v>
       </c>
     </row>
     <row r="10">
@@ -1018,55 +1018,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1260.815420173322</v>
+        <v>1264.467581279454</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4899249076843262</v>
+        <v>0.6931900978088379</v>
       </c>
       <c r="E10" t="n">
-        <v>404</v>
+        <v>338</v>
       </c>
       <c r="F10" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="G10" t="n">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="H10" t="n">
-        <v>2638.064992990645</v>
+        <v>2848.206598201097</v>
       </c>
       <c r="I10" t="n">
-        <v>1.629854202270508</v>
+        <v>11.60828423500061</v>
       </c>
       <c r="J10" t="n">
-        <v>497</v>
+        <v>430</v>
       </c>
       <c r="K10" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L10" t="n">
-        <v>552</v>
+        <v>778</v>
       </c>
       <c r="M10" t="n">
-        <v>6792.788416475796</v>
+        <v>7048.756329238575</v>
       </c>
       <c r="N10" t="n">
-        <v>4.855793952941895</v>
+        <v>6.450820922851562</v>
       </c>
       <c r="O10" t="n">
-        <v>1906</v>
+        <v>1740</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>6131</v>
+        <v>5637</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8143891222763195</v>
+        <v>0.8206112508054247</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6116373967144241</v>
+        <v>0.5959277828364414</v>
       </c>
     </row>
     <row r="11">
@@ -1079,55 +1079,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1174.138809922938</v>
+        <v>1214.21720089738</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5919032096862793</v>
+        <v>1.405348062515259</v>
       </c>
       <c r="E11" t="n">
-        <v>435</v>
+        <v>374</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="H11" t="n">
-        <v>2440.627921420346</v>
+        <v>2674.036562599041</v>
       </c>
       <c r="I11" t="n">
-        <v>1.546383857727051</v>
+        <v>10.75399613380432</v>
       </c>
       <c r="J11" t="n">
-        <v>483</v>
+        <v>430</v>
       </c>
       <c r="K11" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="L11" t="n">
-        <v>528</v>
+        <v>748</v>
       </c>
       <c r="M11" t="n">
-        <v>6797.996765899048</v>
+        <v>6854.574206772943</v>
       </c>
       <c r="N11" t="n">
-        <v>4.39605712890625</v>
+        <v>8.287536144256592</v>
       </c>
       <c r="O11" t="n">
-        <v>1900</v>
+        <v>1730</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>6066</v>
+        <v>5621</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8272816462913313</v>
+        <v>0.8228603025848603</v>
       </c>
       <c r="S11" t="n">
-        <v>0.640978363852227</v>
+        <v>0.6098902015012327</v>
       </c>
     </row>
     <row r="12">
@@ -1140,55 +1140,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1078.074123771012</v>
+        <v>1174.104429416307</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6011650562286377</v>
+        <v>1.190959930419922</v>
       </c>
       <c r="E12" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="G12" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H12" t="n">
-        <v>2452.527239273362</v>
+        <v>2871.52313563783</v>
       </c>
       <c r="I12" t="n">
-        <v>1.735234975814819</v>
+        <v>15.92489290237427</v>
       </c>
       <c r="J12" t="n">
-        <v>473</v>
+        <v>451</v>
       </c>
       <c r="K12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="L12" t="n">
-        <v>526</v>
+        <v>771</v>
       </c>
       <c r="M12" t="n">
-        <v>6871.192949636194</v>
+        <v>6917.958832943517</v>
       </c>
       <c r="N12" t="n">
-        <v>4.602842807769775</v>
+        <v>6.734177112579346</v>
       </c>
       <c r="O12" t="n">
-        <v>1893</v>
+        <v>1756</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5984</v>
+        <v>5563</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8431023358428478</v>
+        <v>0.8302816686585084</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6430711148341112</v>
+        <v>0.5849175739578625</v>
       </c>
     </row>
     <row r="13">
@@ -1201,55 +1201,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1203.27635576212</v>
+        <v>1245.842152203605</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5094132423400879</v>
+        <v>1.923992156982422</v>
       </c>
       <c r="E13" t="n">
-        <v>423</v>
+        <v>368</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="G13" t="n">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="H13" t="n">
-        <v>2525.935668691473</v>
+        <v>2812.046403856298</v>
       </c>
       <c r="I13" t="n">
-        <v>1.612138032913208</v>
+        <v>15.74412703514099</v>
       </c>
       <c r="J13" t="n">
-        <v>500</v>
+        <v>437</v>
       </c>
       <c r="K13" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="L13" t="n">
-        <v>551</v>
+        <v>762</v>
       </c>
       <c r="M13" t="n">
-        <v>6728.420919212201</v>
+        <v>6790.5331376377</v>
       </c>
       <c r="N13" t="n">
-        <v>4.780641078948975</v>
+        <v>6.934466123580933</v>
       </c>
       <c r="O13" t="n">
-        <v>1879</v>
+        <v>1694</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>5968</v>
+        <v>5419</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8211651187983338</v>
+        <v>0.8165324979715791</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6245871506821213</v>
+        <v>0.5858872423035467</v>
       </c>
     </row>
     <row r="14">
@@ -1262,55 +1262,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1233.240785245598</v>
+        <v>1232.878157213494</v>
       </c>
       <c r="D14" t="n">
-        <v>0.425048828125</v>
+        <v>0.9516751766204834</v>
       </c>
       <c r="E14" t="n">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="F14" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="H14" t="n">
-        <v>2514.753255624554</v>
+        <v>2869.775742097329</v>
       </c>
       <c r="I14" t="n">
-        <v>1.748696088790894</v>
+        <v>13.88312792778015</v>
       </c>
       <c r="J14" t="n">
-        <v>494</v>
+        <v>442</v>
       </c>
       <c r="K14" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="L14" t="n">
-        <v>545</v>
+        <v>782</v>
       </c>
       <c r="M14" t="n">
-        <v>6751.491579189738</v>
+        <v>6863.303747926368</v>
       </c>
       <c r="N14" t="n">
-        <v>5.344223976135254</v>
+        <v>7.084908246994019</v>
       </c>
       <c r="O14" t="n">
-        <v>1881</v>
+        <v>1680</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>5989</v>
+        <v>5525</v>
       </c>
       <c r="R14" t="n">
-        <v>0.817338025119243</v>
+        <v>0.8203666626898179</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6275262693986275</v>
+        <v>0.5818667149964937</v>
       </c>
     </row>
     <row r="15">
@@ -1323,55 +1323,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1146.698633237078</v>
+        <v>1334.841282578167</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7114222049713135</v>
+        <v>0.7496800422668457</v>
       </c>
       <c r="E15" t="n">
-        <v>455</v>
+        <v>374</v>
       </c>
       <c r="F15" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="G15" t="n">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="H15" t="n">
-        <v>2326.006576674507</v>
+        <v>2705.243038456235</v>
       </c>
       <c r="I15" t="n">
-        <v>1.778185129165649</v>
+        <v>12.39912390708923</v>
       </c>
       <c r="J15" t="n">
-        <v>488</v>
+        <v>439</v>
       </c>
       <c r="K15" t="n">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="L15" t="n">
-        <v>537</v>
+        <v>758</v>
       </c>
       <c r="M15" t="n">
-        <v>6698.968333569856</v>
+        <v>6938.145000178964</v>
       </c>
       <c r="N15" t="n">
-        <v>4.850774049758911</v>
+        <v>5.352237939834595</v>
       </c>
       <c r="O15" t="n">
-        <v>1868</v>
+        <v>1733</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>5999</v>
+        <v>5634</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8288245926629115</v>
+        <v>0.8076083329847191</v>
       </c>
       <c r="S15" t="n">
-        <v>0.652781374556075</v>
+        <v>0.6100913085001171</v>
       </c>
     </row>
     <row r="16">
@@ -1384,55 +1384,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1200.493778865335</v>
+        <v>1213.376840508191</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6445567607879639</v>
+        <v>0.6784529685974121</v>
       </c>
       <c r="E16" t="n">
-        <v>404</v>
+        <v>341</v>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="H16" t="n">
-        <v>2422.068605261089</v>
+        <v>2809.537863889634</v>
       </c>
       <c r="I16" t="n">
-        <v>2.159656047821045</v>
+        <v>14.57907676696777</v>
       </c>
       <c r="J16" t="n">
-        <v>474</v>
+        <v>407</v>
       </c>
       <c r="K16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="L16" t="n">
-        <v>522</v>
+        <v>730</v>
       </c>
       <c r="M16" t="n">
-        <v>6717.353120596348</v>
+        <v>6858.514583847663</v>
       </c>
       <c r="N16" t="n">
-        <v>4.512831211090088</v>
+        <v>8.567278623580933</v>
       </c>
       <c r="O16" t="n">
-        <v>1860</v>
+        <v>1714</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>5892</v>
+        <v>5531</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8212846998940025</v>
+        <v>0.8230846015308055</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6394311030285595</v>
+        <v>0.5903576744582107</v>
       </c>
     </row>
     <row r="17">
@@ -1445,55 +1445,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1193.362303533648</v>
+        <v>1256.344574038135</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4922361373901367</v>
+        <v>1.294155120849609</v>
       </c>
       <c r="E17" t="n">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G17" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="H17" t="n">
-        <v>2606.951382514447</v>
+        <v>2697.999645965437</v>
       </c>
       <c r="I17" t="n">
-        <v>1.793330907821655</v>
+        <v>12.68989896774292</v>
       </c>
       <c r="J17" t="n">
-        <v>498</v>
+        <v>406</v>
       </c>
       <c r="K17" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="L17" t="n">
-        <v>544</v>
+        <v>724</v>
       </c>
       <c r="M17" t="n">
-        <v>6788.223146738689</v>
+        <v>7018.637523767613</v>
       </c>
       <c r="N17" t="n">
-        <v>4.548931121826172</v>
+        <v>5.249330997467041</v>
       </c>
       <c r="O17" t="n">
-        <v>1883</v>
+        <v>1719</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>6038</v>
+        <v>5518</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8242010791723925</v>
+        <v>0.82099879502486</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6159596810297961</v>
+        <v>0.6155949588749886</v>
       </c>
     </row>
     <row r="18">
@@ -1506,55 +1506,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1122.204902415027</v>
+        <v>1247.481890201382</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5147097110748291</v>
+        <v>0.9917480945587158</v>
       </c>
       <c r="E18" t="n">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="F18" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G18" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="H18" t="n">
-        <v>2626.397912918352</v>
+        <v>2855.945108744185</v>
       </c>
       <c r="I18" t="n">
-        <v>1.624758005142212</v>
+        <v>12.04920792579651</v>
       </c>
       <c r="J18" t="n">
-        <v>492</v>
+        <v>451</v>
       </c>
       <c r="K18" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="L18" t="n">
-        <v>543</v>
+        <v>781</v>
       </c>
       <c r="M18" t="n">
-        <v>6936.785374871602</v>
+        <v>6859.143233228539</v>
       </c>
       <c r="N18" t="n">
-        <v>4.69800329208374</v>
+        <v>4.861671924591064</v>
       </c>
       <c r="O18" t="n">
-        <v>1898</v>
+        <v>1716</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>6195</v>
+        <v>5590</v>
       </c>
       <c r="R18" t="n">
-        <v>0.83822407040584</v>
+        <v>0.8181286134749219</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6213811194977378</v>
+        <v>0.5836294692158052</v>
       </c>
     </row>
     <row r="19">
@@ -1567,55 +1567,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1083.376087894487</v>
+        <v>1210.794742507543</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5700528621673584</v>
+        <v>1.316274881362915</v>
       </c>
       <c r="E19" t="n">
-        <v>399</v>
+        <v>371</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="G19" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="H19" t="n">
-        <v>2567.925408954555</v>
+        <v>2833.988417753593</v>
       </c>
       <c r="I19" t="n">
-        <v>1.609544038772583</v>
+        <v>17.02939796447754</v>
       </c>
       <c r="J19" t="n">
-        <v>498</v>
+        <v>436</v>
       </c>
       <c r="K19" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="L19" t="n">
-        <v>548</v>
+        <v>731</v>
       </c>
       <c r="M19" t="n">
-        <v>6716.798093063316</v>
+        <v>6970.296792734085</v>
       </c>
       <c r="N19" t="n">
-        <v>4.039008855819702</v>
+        <v>5.172549724578857</v>
       </c>
       <c r="O19" t="n">
-        <v>1827</v>
+        <v>1712</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
-        <v>5789</v>
+        <v>5521</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8387064680396856</v>
+        <v>0.8262922256381265</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6176860799781155</v>
+        <v>0.593419261471366</v>
       </c>
     </row>
     <row r="20">
@@ -1628,55 +1628,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1127.61940029762</v>
+        <v>1231.303384382018</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5117297172546387</v>
+        <v>0.6476120948791504</v>
       </c>
       <c r="E20" t="n">
-        <v>401</v>
+        <v>341</v>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="G20" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="H20" t="n">
-        <v>2379.082633431075</v>
+        <v>2521.531229797919</v>
       </c>
       <c r="I20" t="n">
-        <v>1.872286081314087</v>
+        <v>5.402002811431885</v>
       </c>
       <c r="J20" t="n">
-        <v>453</v>
+        <v>381</v>
       </c>
       <c r="K20" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="L20" t="n">
-        <v>515</v>
+        <v>642</v>
       </c>
       <c r="M20" t="n">
-        <v>6788.450239109881</v>
+        <v>6932.85241451354</v>
       </c>
       <c r="N20" t="n">
-        <v>4.386784076690674</v>
+        <v>5.056888103485107</v>
       </c>
       <c r="O20" t="n">
-        <v>1862</v>
+        <v>1719</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>5945</v>
+        <v>5589</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8338914832429447</v>
+        <v>0.8223958465054942</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6495396519628865</v>
+        <v>0.6362923831294555</v>
       </c>
     </row>
     <row r="21">
@@ -1689,55 +1689,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1128.005330158382</v>
+        <v>1393.516321939303</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5185179710388184</v>
+        <v>0.7737691402435303</v>
       </c>
       <c r="E21" t="n">
-        <v>438</v>
+        <v>388</v>
       </c>
       <c r="F21" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="G21" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="H21" t="n">
-        <v>2475.954513103141</v>
+        <v>2944.295094730569</v>
       </c>
       <c r="I21" t="n">
-        <v>1.533375024795532</v>
+        <v>13.51135897636414</v>
       </c>
       <c r="J21" t="n">
-        <v>482</v>
+        <v>446</v>
       </c>
       <c r="K21" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="L21" t="n">
-        <v>525</v>
+        <v>791</v>
       </c>
       <c r="M21" t="n">
-        <v>6821.486508950254</v>
+        <v>6975.3369826401</v>
       </c>
       <c r="N21" t="n">
-        <v>5.111592054367065</v>
+        <v>7.602653980255127</v>
       </c>
       <c r="O21" t="n">
-        <v>1843</v>
+        <v>1740</v>
       </c>
       <c r="P21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>5887</v>
+        <v>5585</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8346393665547294</v>
+        <v>0.8002223655419914</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6370359290669971</v>
+        <v>0.577899232387167</v>
       </c>
     </row>
     <row r="22">
@@ -1750,55 +1750,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1149.582710151814</v>
+        <v>1192.911706201637</v>
       </c>
       <c r="D22" t="n">
-        <v>0.488577127456665</v>
+        <v>1.080287218093872</v>
       </c>
       <c r="E22" t="n">
-        <v>410</v>
+        <v>383</v>
       </c>
       <c r="F22" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G22" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H22" t="n">
-        <v>2485.608362381866</v>
+        <v>2634.406898253947</v>
       </c>
       <c r="I22" t="n">
-        <v>1.747544765472412</v>
+        <v>14.97417688369751</v>
       </c>
       <c r="J22" t="n">
-        <v>472</v>
+        <v>391</v>
       </c>
       <c r="K22" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="L22" t="n">
-        <v>523</v>
+        <v>696</v>
       </c>
       <c r="M22" t="n">
-        <v>6772.351874188213</v>
+        <v>6830.492974379739</v>
       </c>
       <c r="N22" t="n">
-        <v>4.608510255813599</v>
+        <v>4.651046752929688</v>
       </c>
       <c r="O22" t="n">
-        <v>1843</v>
+        <v>1723</v>
       </c>
       <c r="P22" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>5879</v>
+        <v>5564</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8302535468463661</v>
+        <v>0.8253549618342207</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6329770796677912</v>
+        <v>0.6143167252883133</v>
       </c>
     </row>
     <row r="23">
@@ -1811,55 +1811,55 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1093.251523472112</v>
+        <v>1240.250572034548</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4906508922576904</v>
+        <v>0.7166910171508789</v>
       </c>
       <c r="E23" t="n">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="F23" t="n">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G23" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="H23" t="n">
-        <v>2302.417424821325</v>
+        <v>2735.661304552304</v>
       </c>
       <c r="I23" t="n">
-        <v>1.722853899002075</v>
+        <v>10.79982805252075</v>
       </c>
       <c r="J23" t="n">
-        <v>467</v>
+        <v>412</v>
       </c>
       <c r="K23" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="L23" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="M23" t="n">
-        <v>6750.447064188172</v>
+        <v>6882.193585248283</v>
       </c>
       <c r="N23" t="n">
-        <v>4.522751808166504</v>
+        <v>6.407759189605713</v>
       </c>
       <c r="O23" t="n">
-        <v>1872</v>
+        <v>1715</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="n">
-        <v>6045</v>
+        <v>5650</v>
       </c>
       <c r="R23" t="n">
-        <v>0.8380475377294748</v>
+        <v>0.8197884792585641</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6589237123218268</v>
+        <v>0.602501546830056</v>
       </c>
     </row>
     <row r="24">
@@ -1872,55 +1872,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1146.676356712969</v>
+        <v>1341.691321895537</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5228300094604492</v>
+        <v>0.7160778045654297</v>
       </c>
       <c r="E24" t="n">
-        <v>404</v>
+        <v>313</v>
       </c>
       <c r="F24" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="G24" t="n">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="H24" t="n">
-        <v>2408.28054538886</v>
+        <v>2861.430641642539</v>
       </c>
       <c r="I24" t="n">
-        <v>2.243579864501953</v>
+        <v>11.54863524436951</v>
       </c>
       <c r="J24" t="n">
-        <v>485</v>
+        <v>452</v>
       </c>
       <c r="K24" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="L24" t="n">
-        <v>529</v>
+        <v>780</v>
       </c>
       <c r="M24" t="n">
-        <v>6774.668336072777</v>
+        <v>6875.902952217143</v>
       </c>
       <c r="N24" t="n">
-        <v>4.869246006011963</v>
+        <v>5.573902130126953</v>
       </c>
       <c r="O24" t="n">
-        <v>1842</v>
+        <v>1670</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>5886</v>
+        <v>5356</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8307405912984238</v>
+        <v>0.8048705266465538</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6445168344898015</v>
+        <v>0.5838465636400718</v>
       </c>
     </row>
     <row r="25">
@@ -1933,55 +1933,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1227.8705185104</v>
+        <v>1412.97029004664</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5001239776611328</v>
+        <v>1.148900270462036</v>
       </c>
       <c r="E25" t="n">
-        <v>403</v>
+        <v>364</v>
       </c>
       <c r="F25" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="G25" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H25" t="n">
-        <v>2384.212539096379</v>
+        <v>2860.243819493243</v>
       </c>
       <c r="I25" t="n">
-        <v>1.498862028121948</v>
+        <v>11.07990121841431</v>
       </c>
       <c r="J25" t="n">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="K25" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="L25" t="n">
-        <v>512</v>
+        <v>771</v>
       </c>
       <c r="M25" t="n">
-        <v>6989.679213844187</v>
+        <v>6935.04344777503</v>
       </c>
       <c r="N25" t="n">
-        <v>5.260915040969849</v>
+        <v>4.882956981658936</v>
       </c>
       <c r="O25" t="n">
-        <v>1829</v>
+        <v>1734</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>5760</v>
+        <v>5678</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8243309197826413</v>
+        <v>0.7962564617385399</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6588952845827228</v>
+        <v>0.5875665608971931</v>
       </c>
     </row>
     <row r="26">
@@ -1994,55 +1994,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1151.552828598896</v>
+        <v>1222.354806930656</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4741151332855225</v>
+        <v>0.9830410480499268</v>
       </c>
       <c r="E26" t="n">
-        <v>394</v>
+        <v>342</v>
       </c>
       <c r="F26" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="G26" t="n">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="H26" t="n">
-        <v>2459.455754104205</v>
+        <v>2988.419416139492</v>
       </c>
       <c r="I26" t="n">
-        <v>1.74107027053833</v>
+        <v>13.13979196548462</v>
       </c>
       <c r="J26" t="n">
-        <v>541</v>
+        <v>472</v>
       </c>
       <c r="K26" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="L26" t="n">
-        <v>580</v>
+        <v>828</v>
       </c>
       <c r="M26" t="n">
-        <v>6821.083103413869</v>
+        <v>6892.052192264278</v>
       </c>
       <c r="N26" t="n">
-        <v>5.218230009078979</v>
+        <v>4.420008897781372</v>
       </c>
       <c r="O26" t="n">
-        <v>1842</v>
+        <v>1754</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q26" t="n">
-        <v>5852</v>
+        <v>5673</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8311774228314918</v>
+        <v>0.8226428394865259</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6394332517553879</v>
+        <v>0.5663962876697699</v>
       </c>
     </row>
     <row r="27">
@@ -2055,55 +2055,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1111.939717739726</v>
+        <v>1318.396625972192</v>
       </c>
       <c r="D27" t="n">
-        <v>0.554365873336792</v>
+        <v>0.7336070537567139</v>
       </c>
       <c r="E27" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="F27" t="n">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G27" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H27" t="n">
-        <v>2389.601310274144</v>
+        <v>2823.665661345751</v>
       </c>
       <c r="I27" t="n">
-        <v>1.649302005767822</v>
+        <v>11.65166211128235</v>
       </c>
       <c r="J27" t="n">
-        <v>467</v>
+        <v>420</v>
       </c>
       <c r="K27" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="L27" t="n">
-        <v>526</v>
+        <v>739</v>
       </c>
       <c r="M27" t="n">
-        <v>6753.150275545075</v>
+        <v>6946.681274900472</v>
       </c>
       <c r="N27" t="n">
-        <v>4.708034753799438</v>
+        <v>4.64300799369812</v>
       </c>
       <c r="O27" t="n">
-        <v>1910</v>
+        <v>1753</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>6178</v>
+        <v>5651</v>
       </c>
       <c r="R27" t="n">
-        <v>0.8353450356693007</v>
+        <v>0.8102120172497649</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6461501354519658</v>
+        <v>0.5935230724420696</v>
       </c>
     </row>
     <row r="28">
@@ -2116,55 +2116,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1216.097024984794</v>
+        <v>1145.599348375205</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5524218082427979</v>
+        <v>0.7130811214447021</v>
       </c>
       <c r="E28" t="n">
-        <v>414</v>
+        <v>351</v>
       </c>
       <c r="F28" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="H28" t="n">
-        <v>2390.819474188173</v>
+        <v>2704.643092136346</v>
       </c>
       <c r="I28" t="n">
-        <v>1.998072147369385</v>
+        <v>9.338134050369263</v>
       </c>
       <c r="J28" t="n">
-        <v>493</v>
+        <v>420</v>
       </c>
       <c r="K28" t="n">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="L28" t="n">
-        <v>534</v>
+        <v>704</v>
       </c>
       <c r="M28" t="n">
-        <v>6853.605008830117</v>
+        <v>6916.73195182501</v>
       </c>
       <c r="N28" t="n">
-        <v>4.331005811691284</v>
+        <v>5.244277000427246</v>
       </c>
       <c r="O28" t="n">
-        <v>1886</v>
+        <v>1751</v>
       </c>
       <c r="P28" t="n">
         <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>5996</v>
+        <v>5694</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8225609699686535</v>
+        <v>0.8343727418737207</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6511588468976742</v>
+        <v>0.6089709546395369</v>
       </c>
     </row>
     <row r="29">
@@ -2177,55 +2177,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1192.097334391634</v>
+        <v>1236.444768124286</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5494589805603027</v>
+        <v>0.8737099170684814</v>
       </c>
       <c r="E29" t="n">
-        <v>434</v>
+        <v>403</v>
       </c>
       <c r="F29" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G29" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="H29" t="n">
-        <v>2504.678876594258</v>
+        <v>2883.259988508972</v>
       </c>
       <c r="I29" t="n">
-        <v>2.231547832489014</v>
+        <v>10.82199621200562</v>
       </c>
       <c r="J29" t="n">
-        <v>512</v>
+        <v>440</v>
       </c>
       <c r="K29" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="L29" t="n">
-        <v>554</v>
+        <v>769</v>
       </c>
       <c r="M29" t="n">
-        <v>6731.448127448623</v>
+        <v>6956.528761576461</v>
       </c>
       <c r="N29" t="n">
-        <v>4.654663801193237</v>
+        <v>4.45600414276123</v>
       </c>
       <c r="O29" t="n">
-        <v>1829</v>
+        <v>1706</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>5931</v>
+        <v>5640</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8229062585314064</v>
+        <v>0.8222612440052519</v>
       </c>
       <c r="S29" t="n">
-        <v>0.6279138115346973</v>
+        <v>0.5855317950477964</v>
       </c>
     </row>
     <row r="30">
@@ -2238,55 +2238,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1073.739781181712</v>
+        <v>1272.494726416781</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4762248992919922</v>
+        <v>0.7933979034423828</v>
       </c>
       <c r="E30" t="n">
-        <v>397</v>
+        <v>370</v>
       </c>
       <c r="F30" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="G30" t="n">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="H30" t="n">
-        <v>2427.338609129287</v>
+        <v>2765.838256711751</v>
       </c>
       <c r="I30" t="n">
-        <v>1.537328958511353</v>
+        <v>9.719172954559326</v>
       </c>
       <c r="J30" t="n">
-        <v>478</v>
+        <v>420</v>
       </c>
       <c r="K30" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="L30" t="n">
-        <v>525</v>
+        <v>740</v>
       </c>
       <c r="M30" t="n">
-        <v>6700.662414460754</v>
+        <v>7066.583546302754</v>
       </c>
       <c r="N30" t="n">
-        <v>5.182881832122803</v>
+        <v>5.45979118347168</v>
       </c>
       <c r="O30" t="n">
-        <v>1847</v>
+        <v>1753</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>5927</v>
+        <v>5618</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8397561741262378</v>
+        <v>0.8199278734796036</v>
       </c>
       <c r="S30" t="n">
-        <v>0.6377464705741887</v>
+        <v>0.6086031901287233</v>
       </c>
     </row>
     <row r="31">
@@ -2299,55 +2299,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1110.197151285881</v>
+        <v>1341.420121453891</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5489411354064941</v>
+        <v>0.7903761863708496</v>
       </c>
       <c r="E31" t="n">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="F31" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="G31" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H31" t="n">
-        <v>2522.059126536623</v>
+        <v>2811.849657971881</v>
       </c>
       <c r="I31" t="n">
-        <v>1.686222076416016</v>
+        <v>10.53063797950745</v>
       </c>
       <c r="J31" t="n">
-        <v>480</v>
+        <v>439</v>
       </c>
       <c r="K31" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="L31" t="n">
-        <v>529</v>
+        <v>741</v>
       </c>
       <c r="M31" t="n">
-        <v>6741.391749005619</v>
+        <v>7079.093963344251</v>
       </c>
       <c r="N31" t="n">
-        <v>5.233093023300171</v>
+        <v>5.160303115844727</v>
       </c>
       <c r="O31" t="n">
-        <v>1861</v>
+        <v>1742</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>5998</v>
+        <v>5685</v>
       </c>
       <c r="R31" t="n">
-        <v>0.8353163274557306</v>
+        <v>0.8105096318257955</v>
       </c>
       <c r="S31" t="n">
-        <v>0.6258845027202823</v>
+        <v>0.6027952627085165</v>
       </c>
     </row>
   </sheetData>
